--- a/assets/docs/lop3/Tin hoc - Lop 3.xlsx
+++ b/assets/docs/lop3/Tin hoc - Lop 3.xlsx
@@ -1067,11 +1067,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS làm bài ôn tương tác và tự nhận ra phần kiến thức mình còn chưa chắc.</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
